--- a/StructureDefinition-ServiceRequestReferenciadaLE.xlsx
+++ b/StructureDefinition-ServiceRequestReferenciadaLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1243,7 +1243,7 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>http://minsal.cl/listaespera/ValueSet/VSMotivoDerivacion</t>
+    <t>http://minsal.cl/listaespera/ValueSet/VSDestinoReferenciaCodigo</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>84</v>
